--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,22 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,22 +768,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,12 +790,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -816,12 +812,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -838,18 +834,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -860,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,15 +882,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>3</v>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1092,26 +1092,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1122,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1686,26 +1686,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,26 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2098,14 +2098,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+          <t>Continuing Jobless ClaimsDEC/28</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1848K</t>
+        </is>
+      </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -2116,22 +2128,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>16.5M</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2146,24 +2154,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
         <v>2</v>
       </c>
@@ -2176,18 +2172,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2202,26 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2306,22 +2306,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2332,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,22 +2350,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2380,12 +2372,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2428,18 +2420,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2450,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2472,18 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,18 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2916,22 +2916,18 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -2946,26 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3036,18 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3062,22 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3092,26 +3092,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3122,18 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3562,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3592,18 +3592,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,18 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,12 +3648,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3659,11 +3663,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3674,26 +3678,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3712,14 +3716,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3988,18 +3988,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4274,18 +4274,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4296,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4318,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4340,18 +4348,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4362,12 +4374,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4384,19 +4396,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>3</v>
@@ -4410,22 +4418,18 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -4436,22 +4440,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4556,22 +4556,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -4586,18 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4612,24 +4612,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4642,18 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4664,16 +4664,24 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4686,16 +4694,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4708,22 +4720,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4738,26 +4750,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -4768,24 +4772,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4798,18 +4794,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4820,22 +4824,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4850,20 +4854,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,24 +4876,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4906,26 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4936,16 +4928,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4958,22 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -6054,18 +6054,18 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexJAN</t>
+          <t>Kansas Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -6080,18 +6080,18 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexJAN</t>
+          <t>Kansas Fed Composite IndexJAN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,22 +6172,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,15 +6194,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6224,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,18 +6264,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,19 +6334,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,18 +6356,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,18 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6504,22 +6508,18 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6870,22 +6870,18 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6900,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -7178,22 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7208,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7260,26 +7260,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7286,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7812,18 +7812,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7834,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7856,18 +7860,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7878,22 +7886,22 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7904,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7926,19 +7934,15 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>3</v>
@@ -7952,22 +7956,18 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
           <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>1.1%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,26 +8100,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8126,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,22 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -8182,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8212,18 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,22 +8242,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -8264,26 +8272,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,14 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -8534,22 +8546,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8564,26 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8594,22 +8598,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8624,22 +8628,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8654,22 +8658,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8684,22 +8688,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8714,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -8744,18 +8748,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8770,20 +8778,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="n">
         <v>2</v>
       </c>
@@ -8904,22 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9206,22 +9206,26 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -9232,26 +9236,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9288,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9590,14 +9590,26 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
@@ -9608,18 +9620,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9634,22 +9646,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9664,18 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -9902,15 +9902,19 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>3</v>
@@ -9924,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9946,22 +9950,18 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,22 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10536,26 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10566,18 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>141K</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10592,26 +10596,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -10652,26 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10682,22 +10678,26 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10738,22 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -10764,22 +10768,18 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,26 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10904,26 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -10934,18 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10990,18 +10990,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,22 +11016,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F426" t="n">
@@ -11046,26 +11046,26 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,14 +11492,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,14 +11998,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12020,14 +12024,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12042,22 +12046,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12068,22 +12072,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -12094,22 +12098,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12120,14 +12120,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,22 +12146,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12168,14 +12168,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -12360,18 +12360,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12382,18 +12382,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12404,22 +12408,22 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -12430,18 +12434,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12452,18 +12460,22 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -12474,22 +12486,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -12500,22 +12508,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -12526,18 +12530,14 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F497" t="n">
@@ -12552,14 +12552,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F498" t="n">
@@ -13234,14 +13234,18 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13252,18 +13256,14 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -13568,18 +13568,22 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -13590,18 +13594,22 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -13612,22 +13620,18 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -13638,22 +13642,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -14114,16 +14114,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E575" t="inlineStr"/>
       <c r="F575" t="n">
         <v>3</v>
       </c>
@@ -14136,7 +14132,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14154,22 +14150,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E577" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" t="inlineStr"/>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -14180,22 +14168,22 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F578" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -14206,7 +14194,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
@@ -14242,12 +14230,20 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -14260,18 +14256,18 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F582" t="n">
@@ -14286,12 +14282,16 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -15398,22 +15398,18 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -15424,18 +15420,18 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -15450,22 +15446,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15476,22 +15472,22 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F642" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
@@ -15502,22 +15498,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
@@ -15550,18 +15546,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15576,18 +15572,22 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
@@ -16110,14 +16110,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -17244,7 +17244,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
@@ -17490,12 +17490,20 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr"/>
-      <c r="E751" t="inlineStr"/>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F751" t="n">
         <v>3</v>
       </c>
@@ -17636,22 +17644,22 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F758" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="759">
@@ -17680,14 +17688,14 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr"/>
       <c r="E760" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F760" t="n">
@@ -17720,14 +17728,14 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F762" t="n">
@@ -17760,22 +17768,22 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F764" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="765">
@@ -17838,20 +17846,12 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E767" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D767" t="inlineStr"/>
+      <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
         <v>3</v>
       </c>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -18322,14 +18322,14 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr"/>
       <c r="F793" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="794">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
@@ -18358,18 +18358,14 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr"/>
-      <c r="E795" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E795" t="inlineStr"/>
       <c r="F795" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="796">
@@ -18380,7 +18376,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
@@ -18398,14 +18394,18 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr"/>
-      <c r="E797" t="inlineStr"/>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F797" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="798">
@@ -18416,14 +18416,14 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr"/>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="799">
@@ -18434,7 +18434,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
@@ -18452,14 +18452,14 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr"/>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="801">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
@@ -18524,7 +18524,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>Fed Beige Book</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Fed Beige Book</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
@@ -19238,14 +19238,14 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr"/>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="844">
@@ -19256,14 +19256,14 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr"/>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="845">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19292,14 +19292,14 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
       <c r="D846" t="inlineStr"/>
       <c r="E846" t="inlineStr"/>
       <c r="F846" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="847">
@@ -19310,16 +19310,12 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
       <c r="D847" t="inlineStr"/>
-      <c r="E847" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="E847" t="inlineStr"/>
       <c r="F847" t="n">
         <v>3</v>
       </c>
@@ -19332,18 +19328,14 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C848" t="inlineStr"/>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D848" t="inlineStr"/>
       <c r="E848" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F848" t="n">
@@ -19358,14 +19350,22 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C849" t="inlineStr"/>
-      <c r="D849" t="inlineStr"/>
-      <c r="E849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="F849" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="850">
@@ -19484,14 +19484,14 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Government PayrollsFEB</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
       <c r="D856" t="inlineStr"/>
       <c r="E856" t="inlineStr"/>
       <c r="F856" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="857">
@@ -19502,18 +19502,18 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Average Weekly HoursFEB</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr"/>
       <c r="E857" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="F857" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="858">
@@ -19524,14 +19524,18 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
       <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
       <c r="F858" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="859">
@@ -19542,14 +19546,14 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Nonfarm Payrolls PrivateFEB</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
       <c r="D859" t="inlineStr"/>
       <c r="E859" t="inlineStr"/>
       <c r="F859" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="860">
@@ -19560,14 +19564,14 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Manufacturing PayrollsFEB</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
       <c r="D860" t="inlineStr"/>
       <c r="E860" t="inlineStr"/>
       <c r="F860" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="861">
@@ -19578,14 +19582,14 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
       <c r="D861" t="inlineStr"/>
       <c r="E861" t="inlineStr"/>
       <c r="F861" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="862">
@@ -19596,14 +19600,14 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr"/>
       <c r="E862" t="inlineStr"/>
       <c r="F862" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="863">
@@ -19614,18 +19618,18 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
       <c r="D863" t="inlineStr"/>
       <c r="E863" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="F863" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="864">
@@ -19636,18 +19640,14 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Average Weekly HoursFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
       <c r="D864" t="inlineStr"/>
-      <c r="E864" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
+      <c r="E864" t="inlineStr"/>
       <c r="F864" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="865">
@@ -19658,14 +19658,14 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Government PayrollsFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="866">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,15 +742,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>3</v>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -860,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,22 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,26 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2098,26 +2098,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2128,18 +2128,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2154,14 +2158,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>Continuing Jobless ClaimsDEC/28</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1848K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,22 +2188,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>16.5M</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2202,24 +2214,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>2</v>
       </c>
@@ -2306,18 +2306,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2328,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2350,12 +2358,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2372,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2420,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,18 +2860,18 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2916,18 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -2942,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3036,18 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3062,22 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3092,26 +3092,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3122,18 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3540,14 +3540,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3562,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3577,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3592,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,26 +3618,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,26 +3678,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3708,18 +3708,18 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3988,18 +3988,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4274,22 +4274,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4300,19 +4296,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,18 +4318,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4348,22 +4344,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
@@ -4374,15 +4366,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>3</v>
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,22 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4612,16 +4616,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,26 +4642,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,24 +4672,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4694,20 +4694,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4720,22 +4716,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -4750,18 +4746,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -4772,16 +4776,20 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4794,26 +4802,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4854,16 +4854,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,18 +4884,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4898,24 +4914,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4928,18 +4936,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4954,22 +4962,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4984,24 +4992,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5044,22 +5044,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -6054,18 +6054,18 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexJAN</t>
+          <t>Kansas Fed Composite IndexJAN</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -6080,18 +6080,18 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexJAN</t>
+          <t>Kansas Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,18 +6172,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6194,19 +6198,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,22 +6264,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6290,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6308,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,15 +6330,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6356,22 +6356,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6448,22 +6448,18 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6508,18 +6504,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6870,18 +6870,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6896,22 +6900,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -7178,18 +7178,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,26 +7208,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7260,22 +7260,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7286,22 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7812,22 +7812,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7838,12 +7834,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,22 +7856,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7886,19 +7882,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7912,12 +7904,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8070,22 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8100,22 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8126,18 +8126,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,26 +8156,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8182,26 +8186,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,22 +8212,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8242,26 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8272,18 +8264,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
           <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>1.1%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8298,22 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -8428,12 +8428,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8516,22 +8516,22 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -8546,20 +8546,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8572,18 +8564,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8628,22 +8624,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,22 +8654,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8688,22 +8684,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8718,26 +8714,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8748,22 +8740,18 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8778,14 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,22 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9206,26 +9206,22 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -9236,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9262,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9288,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9590,22 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9620,22 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,14 +9634,26 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9664,18 +9664,18 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -9902,22 +9902,22 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,22 +10042,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10068,12 +10064,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,15 +10086,19 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
         <v>3</v>
@@ -10536,26 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -10566,22 +10566,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>111K</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>141K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10596,22 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>62.6%</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10622,26 +10622,26 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -10652,22 +10652,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10678,26 +10682,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -10708,26 +10708,26 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -10738,26 +10738,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10768,18 +10764,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>141K</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,26 +10794,26 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10904,26 +10904,26 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10934,18 +10934,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -10990,18 +10990,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -11016,26 +11016,26 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -11046,22 +11046,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,14 +11492,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,22 +12002,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -12024,14 +12028,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12046,22 +12050,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12072,22 +12072,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12098,14 +12094,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12120,22 +12116,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -12146,14 +12142,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12168,14 +12168,14 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -12360,14 +12360,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -12382,18 +12382,14 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F491" t="n">
@@ -12408,22 +12404,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12434,22 +12426,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12460,22 +12448,22 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12486,18 +12474,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12508,18 +12500,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12530,18 +12526,18 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12552,18 +12548,22 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -13234,18 +13234,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -13256,14 +13252,18 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13568,22 +13568,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549">
@@ -13594,22 +13590,18 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F549" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -13620,18 +13612,22 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -13642,18 +13638,22 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1.4M</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14150,12 +14150,16 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F577" t="n">
         <v>3</v>
       </c>
@@ -14168,18 +14172,18 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F578" t="n">
@@ -14194,12 +14198,20 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14230,22 +14242,22 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F581" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="582">
@@ -14256,22 +14268,14 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D582" t="inlineStr"/>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
@@ -14282,16 +14286,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -15398,18 +15398,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15546,22 +15550,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D645" t="inlineStr"/>
       <c r="E645" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="646">
@@ -15572,18 +15572,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F646" t="n">
@@ -16110,14 +16110,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="676">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -17244,7 +17244,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
@@ -17490,20 +17490,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D751" t="inlineStr"/>
+      <c r="E751" t="inlineStr"/>
       <c r="F751" t="n">
         <v>3</v>
       </c>
@@ -17644,22 +17636,22 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
       <c r="D758" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F758" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="759">
@@ -17688,14 +17680,14 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr"/>
       <c r="E760" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F760" t="n">
@@ -17728,14 +17720,14 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F762" t="n">
@@ -17768,22 +17760,22 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F764" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17846,12 +17838,20 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F767" t="n">
         <v>3</v>
       </c>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
@@ -18358,14 +18358,14 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr"/>
       <c r="F795" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="796">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
@@ -18394,18 +18394,14 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr"/>
-      <c r="E797" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E797" t="inlineStr"/>
       <c r="F797" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="798">
@@ -18416,14 +18412,18 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr"/>
-      <c r="E798" t="inlineStr"/>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F798" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="799">
@@ -18434,14 +18434,14 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr"/>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="800">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
@@ -18470,14 +18470,14 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="802">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
@@ -18524,7 +18524,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Fed Beige Book</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>Fed Beige Book</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
@@ -19238,14 +19238,22 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
-      <c r="D843" t="inlineStr"/>
-      <c r="E843" t="inlineStr"/>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="F843" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="844">
@@ -19256,14 +19264,14 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr"/>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="845">
@@ -19274,14 +19282,14 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
       <c r="D845" t="inlineStr"/>
       <c r="E845" t="inlineStr"/>
       <c r="F845" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="846">
@@ -19292,7 +19300,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19310,14 +19318,14 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
       <c r="D847" t="inlineStr"/>
       <c r="E847" t="inlineStr"/>
       <c r="F847" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="848">
@@ -19328,16 +19336,12 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C848" t="inlineStr"/>
       <c r="D848" t="inlineStr"/>
-      <c r="E848" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="E848" t="inlineStr"/>
       <c r="F848" t="n">
         <v>3</v>
       </c>
@@ -19350,18 +19354,14 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C849" t="inlineStr"/>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D849" t="inlineStr"/>
       <c r="E849" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F849" t="n">
@@ -19484,14 +19484,14 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Government PayrollsFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
       <c r="D856" t="inlineStr"/>
       <c r="E856" t="inlineStr"/>
       <c r="F856" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="857">
@@ -19502,18 +19502,14 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Average Weekly HoursFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
+      <c r="E857" t="inlineStr"/>
       <c r="F857" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="858">
@@ -19524,18 +19520,18 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
       <c r="D858" t="inlineStr"/>
       <c r="E858" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="F858" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="859">
@@ -19546,14 +19542,14 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
       <c r="D859" t="inlineStr"/>
       <c r="E859" t="inlineStr"/>
       <c r="F859" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="860">
@@ -19564,14 +19560,14 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
       <c r="D860" t="inlineStr"/>
       <c r="E860" t="inlineStr"/>
       <c r="F860" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="861">
@@ -19582,14 +19578,14 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Nonfarm Payrolls PrivateFEB</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
       <c r="D861" t="inlineStr"/>
       <c r="E861" t="inlineStr"/>
       <c r="F861" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="862">
@@ -19600,14 +19596,18 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr"/>
-      <c r="E862" t="inlineStr"/>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
       <c r="F862" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="863">
@@ -19618,18 +19618,18 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Average Weekly HoursFEB</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
       <c r="D863" t="inlineStr"/>
       <c r="E863" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="F863" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="864">
@@ -19640,14 +19640,14 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Government PayrollsFEB</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
       <c r="D864" t="inlineStr"/>
       <c r="E864" t="inlineStr"/>
       <c r="F864" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="865">
@@ -19658,14 +19658,14 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Manufacturing PayrollsFEB</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="866">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F879"/>
+  <dimension ref="A1:F880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,18 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,22 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,12 +794,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,15 +838,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -856,22 +864,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +886,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1092,26 +1092,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1122,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,26 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2098,26 +2098,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2128,22 +2128,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>16.5M</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2158,14 +2154,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>Continuing Jobless ClaimsDEC/28</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1848K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2176,18 +2184,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2202,24 +2214,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>2</v>
       </c>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,22 +2328,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2354,22 +2350,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2380,12 +2372,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2428,18 +2420,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2450,18 +2446,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,22 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2886,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2916,22 +2920,18 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,18 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3036,18 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3062,22 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3092,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3122,18 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3562,26 +3562,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3600,14 +3600,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3622,18 +3618,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,12 +3644,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3663,11 +3659,11 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3678,18 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3704,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3944,18 +3944,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,18 +4252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4274,22 +4278,18 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -4300,15 +4300,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4322,12 +4326,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4344,12 +4348,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4366,22 +4370,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4392,19 +4392,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
         <v>3</v>
@@ -4418,12 +4414,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,18 +4436,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -4556,26 +4556,18 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,20 +4578,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
         <v>3</v>
       </c>
@@ -4612,26 +4600,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4642,26 +4630,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4672,22 +4652,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4698,22 +4682,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -4728,12 +4708,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4750,18 +4730,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -4772,26 +4760,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4802,24 +4790,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4832,26 +4812,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4862,16 +4842,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4884,22 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4910,26 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4940,16 +4928,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4962,22 +4954,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4992,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5538,22 +5538,18 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
@@ -5564,18 +5560,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6194,15 +6202,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6216,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6238,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6260,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6282,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6304,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6326,19 +6338,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6352,22 +6360,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6448,22 +6448,18 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6478,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6870,22 +6870,18 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6900,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -7178,22 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7208,26 +7204,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -7238,18 +7230,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7264,22 +7256,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7286,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7856,19 +7864,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7904,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7926,22 +7934,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7952,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7974,22 +7978,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8070,26 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -8100,22 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8156,18 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,22 +8186,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8212,22 +8212,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8238,22 +8242,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,26 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8298,18 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8516,14 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+          <t>Personal Spending MoMDEC</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -8534,26 +8546,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8564,26 +8576,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8594,26 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8624,22 +8632,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8684,22 +8688,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -8714,18 +8718,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8740,26 +8748,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8770,20 +8778,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="n">
         <v>2</v>
       </c>
@@ -8904,22 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -8934,22 +8934,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8986,26 +8990,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9206,26 +9206,22 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -9236,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9262,18 +9262,18 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -9590,14 +9590,26 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
@@ -9608,18 +9620,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9634,22 +9646,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9664,18 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -9902,15 +9902,19 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>3</v>
@@ -9924,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9950,18 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9972,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,12 +9998,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10016,19 +10020,15 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>3</v>
@@ -10042,18 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10064,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10086,22 +10090,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10196,22 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,22 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -10252,26 +10256,26 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -10282,22 +10286,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -10312,22 +10316,18 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>1886K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -10536,26 +10536,26 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10566,26 +10566,26 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10596,18 +10596,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>141K</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10622,22 +10626,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>-2K</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10652,26 +10652,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10682,18 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,22 +10708,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10734,22 +10734,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -10764,22 +10764,22 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F416" t="n">
@@ -10794,22 +10794,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11590,18 +11590,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11612,18 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11638,22 +11642,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="462">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -11976,14 +11976,14 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,22 +11998,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -12024,14 +12020,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12046,18 +12046,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12068,22 +12072,22 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -12094,22 +12098,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -12120,22 +12120,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -12146,18 +12142,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12172,18 +12164,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12190,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12360,22 +12360,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12386,18 +12382,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -12408,18 +12408,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -12430,18 +12430,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -12452,18 +12456,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F494" t="n">
@@ -12478,22 +12478,18 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -12504,14 +12500,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F496" t="n">
@@ -12526,22 +12522,22 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -12552,18 +12548,22 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12574,18 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12596,18 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,14 +12622,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12644,18 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -12841,7 +12841,11 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr"/>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
       <c r="D511" t="inlineStr">
         <is>
           <t>-1</t>
@@ -12867,11 +12871,7 @@
           <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
-      </c>
+      <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr">
         <is>
           <t>-1</t>
@@ -12897,7 +12897,11 @@
           <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="D513" t="inlineStr">
         <is>
           <t>47</t>
@@ -13000,7 +13004,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -13036,7 +13040,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13108,14 +13112,14 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="525">
@@ -13144,14 +13148,14 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr"/>
       <c r="F526" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -13180,18 +13184,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -13202,14 +13202,18 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
-      <c r="D529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -13238,18 +13242,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -13278,14 +13278,18 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -13476,14 +13480,14 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F544" t="n">
@@ -13520,22 +13524,18 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>1.4M</t>
-        </is>
-      </c>
+      <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -13546,18 +13546,18 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.4M</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F547" t="n">
@@ -13572,18 +13572,22 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -13620,22 +13624,18 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -13646,18 +13646,22 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -13990,14 +13994,22 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -14008,16 +14020,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
         <v>3</v>
       </c>
@@ -14030,18 +14038,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F571" t="n">
@@ -14056,22 +14060,22 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F572" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573">
@@ -14082,14 +14086,22 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
-      <c r="E573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -14100,7 +14112,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -14136,7 +14148,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14154,7 +14166,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14172,22 +14184,14 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="579">
@@ -14198,7 +14202,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
@@ -14216,16 +14220,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -14238,18 +14238,14 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F581" t="n">
@@ -14264,22 +14260,22 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F582" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
@@ -14290,14 +14286,22 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F583" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="584">
@@ -14450,7 +14454,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
@@ -14468,7 +14472,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
@@ -14504,7 +14508,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14522,14 +14526,14 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -14540,7 +14544,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14558,7 +14562,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14576,7 +14580,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14594,14 +14598,14 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -14612,14 +14616,14 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr"/>
       <c r="E600" t="inlineStr"/>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14630,14 +14634,14 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr"/>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14666,7 +14670,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -14684,7 +14688,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
@@ -14702,7 +14706,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
@@ -14720,7 +14724,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14738,7 +14742,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14756,7 +14760,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14774,7 +14778,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14792,7 +14796,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14810,7 +14814,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14846,7 +14850,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14864,14 +14868,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
@@ -14882,14 +14886,14 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
@@ -15098,11 +15102,15 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
-      <c r="D627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="E627" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15120,14 +15128,18 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
-      <c r="D628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F628" t="n">
@@ -15142,18 +15154,14 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
-      <c r="D629" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D629" t="inlineStr"/>
       <c r="E629" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F629" t="n">
@@ -15168,15 +15176,11 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="D630" t="inlineStr"/>
       <c r="E630" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -15246,18 +15250,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15272,22 +15276,22 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F634" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="635">
@@ -15298,22 +15302,22 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.12M</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="636">
@@ -15324,22 +15328,18 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D636" t="inlineStr"/>
       <c r="E636" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F636" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
@@ -15350,22 +15350,22 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F637" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -15376,18 +15376,22 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr"/>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15424,18 +15428,22 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -15446,22 +15454,22 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F641" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15498,22 +15506,18 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -15524,22 +15528,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
@@ -15550,18 +15554,18 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F645" t="n">
@@ -15576,18 +15580,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F646" t="n">
@@ -15656,7 +15660,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15692,7 +15696,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15715,7 +15719,11 @@
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
-      <c r="E653" t="inlineStr"/>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
       <c r="F653" t="n">
         <v>2</v>
       </c>
@@ -15769,7 +15777,11 @@
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr"/>
-      <c r="E656" t="inlineStr"/>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F656" t="n">
         <v>2</v>
       </c>
@@ -15782,7 +15794,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15800,7 +15812,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15926,18 +15938,14 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E665" t="inlineStr"/>
       <c r="F665" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="666">
@@ -15948,7 +15956,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15966,7 +15974,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -16002,7 +16010,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -16020,18 +16028,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="671">
@@ -16042,14 +16046,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr"/>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F671" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="672">
@@ -16096,14 +16104,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16114,12 +16126,16 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr"/>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="F675" t="n">
         <v>3</v>
       </c>
@@ -16137,7 +16153,11 @@
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
       <c r="F676" t="n">
         <v>3</v>
       </c>
@@ -16150,12 +16170,16 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr"/>
-      <c r="E677" t="inlineStr"/>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="F677" t="n">
         <v>3</v>
       </c>
@@ -16186,14 +16210,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -16204,7 +16228,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16222,7 +16246,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16240,14 +16264,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -16258,12 +16282,16 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr"/>
-      <c r="E683" t="inlineStr"/>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="F683" t="n">
         <v>3</v>
       </c>
@@ -16281,7 +16309,11 @@
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr"/>
-      <c r="E684" t="inlineStr"/>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="F684" t="n">
         <v>3</v>
       </c>
@@ -16312,7 +16344,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16330,7 +16362,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16366,7 +16398,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -16438,14 +16470,14 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
       <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="694">
@@ -16456,14 +16488,14 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="695">
@@ -16474,7 +16506,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -16492,7 +16524,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16510,7 +16542,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16528,7 +16560,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16546,7 +16578,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16582,7 +16614,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16600,7 +16632,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16654,7 +16686,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16672,7 +16704,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C706" t="inlineStr"/>
@@ -16726,7 +16758,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16762,14 +16794,14 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="712">
@@ -16780,14 +16812,14 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="713">
@@ -16798,14 +16830,14 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr"/>
       <c r="F713" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="714">
@@ -16816,7 +16848,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
@@ -16834,7 +16866,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C715" t="inlineStr"/>
@@ -16852,7 +16884,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
@@ -16870,7 +16902,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
@@ -16888,7 +16920,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -16906,14 +16938,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="720">
@@ -16924,14 +16956,14 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr"/>
       <c r="F720" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="721">
@@ -16942,7 +16974,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -16960,14 +16992,14 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
       <c r="F722" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="723">
@@ -16978,7 +17010,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C723" t="inlineStr"/>
@@ -16996,7 +17028,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C724" t="inlineStr"/>
@@ -17032,7 +17064,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C726" t="inlineStr"/>
@@ -17050,7 +17082,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -17068,7 +17100,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -17086,7 +17118,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -17104,7 +17136,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17122,7 +17154,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17140,7 +17172,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17158,7 +17190,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -17176,7 +17208,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -17230,7 +17262,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17248,7 +17280,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -17266,7 +17298,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -17284,7 +17316,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -17302,7 +17334,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -17320,7 +17352,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17338,7 +17370,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17356,7 +17388,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17374,14 +17406,14 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr"/>
       <c r="F745" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="746">
@@ -17392,22 +17424,22 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="747">
@@ -17418,14 +17450,18 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
-      <c r="E747" t="inlineStr"/>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F747" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="748">
@@ -17436,22 +17472,14 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
-      <c r="D748" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E748" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="inlineStr"/>
       <c r="F748" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="749">
@@ -17462,14 +17490,14 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr"/>
       <c r="F749" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="750">
@@ -17480,22 +17508,14 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E750" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr"/>
       <c r="F750" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="751">
@@ -17506,14 +17526,18 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
-      <c r="E751" t="inlineStr"/>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F751" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="752">
@@ -17524,18 +17548,22 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="753">
@@ -17546,20 +17574,12 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E753" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr"/>
       <c r="F753" t="n">
         <v>3</v>
       </c>
@@ -17572,14 +17592,18 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
-      <c r="D754" t="inlineStr"/>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F754" t="n">
@@ -17594,12 +17618,20 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr"/>
-      <c r="E755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F755" t="n">
         <v>3</v>
       </c>
@@ -17612,14 +17644,14 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="757">
@@ -17630,14 +17662,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758">
@@ -17648,22 +17680,14 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
-      <c r="D758" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E758" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
       <c r="F758" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="759">
@@ -17674,22 +17698,18 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F759" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="760">
@@ -17718,14 +17738,22 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr"/>
-      <c r="E761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F761" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="762">
@@ -17736,14 +17764,14 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="763">
@@ -17754,14 +17782,14 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="764">
@@ -17772,14 +17800,22 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F764" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765">
@@ -17790,18 +17826,14 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E765" t="inlineStr"/>
       <c r="F765" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="766">
@@ -17812,22 +17844,22 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F766" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="767">
@@ -17838,14 +17870,14 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr"/>
       <c r="F767" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="768">
@@ -17856,16 +17888,12 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr"/>
-      <c r="E768" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E768" t="inlineStr"/>
       <c r="F768" t="n">
         <v>3</v>
       </c>
@@ -17878,18 +17906,14 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F769" t="n">
@@ -17904,14 +17928,22 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr"/>
-      <c r="E770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F770" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="771">
@@ -17940,7 +17972,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -17958,7 +17990,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
@@ -18012,15 +18044,11 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
-      <c r="D776" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D776" t="inlineStr"/>
       <c r="E776" t="inlineStr"/>
       <c r="F776" t="n">
         <v>3</v>
@@ -18034,11 +18062,15 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/21</t>
+          <t>NY Fed Treasury Purchases 4 to 6 yrs</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
-      <c r="D777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="n">
         <v>3</v>
@@ -18074,12 +18106,16 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
       <c r="D779" t="inlineStr"/>
-      <c r="E779" t="inlineStr"/>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F779" t="n">
         <v>3</v>
       </c>
@@ -18128,12 +18164,16 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
       <c r="D782" t="inlineStr"/>
-      <c r="E782" t="inlineStr"/>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F782" t="n">
         <v>3</v>
       </c>
@@ -18146,7 +18186,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18164,7 +18204,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -18182,7 +18222,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -18200,7 +18240,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
@@ -18218,7 +18258,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
@@ -18236,7 +18276,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18254,7 +18294,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
@@ -18272,7 +18312,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
@@ -18326,14 +18366,14 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr"/>
       <c r="F793" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="794">
@@ -18344,7 +18384,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
@@ -18362,14 +18402,14 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr"/>
       <c r="F795" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="796">
@@ -18380,12 +18420,16 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
       <c r="D796" t="inlineStr"/>
-      <c r="E796" t="inlineStr"/>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F796" t="n">
         <v>1</v>
       </c>
@@ -18398,16 +18442,12 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr"/>
-      <c r="E797" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E797" t="inlineStr"/>
       <c r="F797" t="n">
         <v>1</v>
       </c>
@@ -18420,14 +18460,14 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr"/>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="799">
@@ -18438,12 +18478,16 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr"/>
-      <c r="E799" t="inlineStr"/>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F799" t="n">
         <v>2</v>
       </c>
@@ -18456,12 +18500,16 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr"/>
-      <c r="E800" t="inlineStr"/>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F800" t="n">
         <v>2</v>
       </c>
@@ -18474,14 +18522,14 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="802">
@@ -18510,14 +18558,14 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="804">
@@ -18528,7 +18576,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -18546,14 +18594,18 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr"/>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F805" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="806">
@@ -18582,18 +18634,14 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E807" t="inlineStr"/>
       <c r="F807" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="808">
@@ -18604,7 +18652,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
@@ -18622,14 +18670,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="810">
@@ -18640,14 +18688,14 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
       <c r="E810" t="inlineStr"/>
       <c r="F810" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="811">
@@ -18671,19 +18719,19 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2025-02-28 13:00:00-05:00</t>
+          <t>2025-02-28 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Chicago PMIFEB</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
       <c r="D812" t="inlineStr"/>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="813">
@@ -18694,7 +18742,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
@@ -18707,37 +18755,37 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2025-03-03 09:45:00-05:00</t>
+          <t>2025-02-28 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C814" t="inlineStr"/>
       <c r="D814" t="inlineStr"/>
       <c r="E814" t="inlineStr"/>
       <c r="F814" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2025-03-03 10:00:00-05:00</t>
+          <t>2025-03-03 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FinalFEB</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
       <c r="D815" t="inlineStr"/>
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="816">
@@ -18748,14 +18796,18 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
       <c r="D816" t="inlineStr"/>
-      <c r="E816" t="inlineStr"/>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F816" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="817">
@@ -18766,7 +18818,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -18784,18 +18836,14 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
       <c r="D818" t="inlineStr"/>
-      <c r="E818" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E818" t="inlineStr"/>
       <c r="F818" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="819">
@@ -18806,7 +18854,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
@@ -18819,12 +18867,12 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>2025-03-04 08:55:00-05:00</t>
+          <t>2025-03-03 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Redbook YoYMAR/01</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
@@ -18837,21 +18885,17 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>2025-03-04 10:00:00-05:00</t>
+          <t>2025-03-04 08:55:00-05:00</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RCM/TIPP Economic Optimism IndexMAR</t>
+          <t>Redbook YoYMAR/01</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
       <c r="D821" t="inlineStr"/>
-      <c r="E821" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="E821" t="inlineStr"/>
       <c r="F821" t="n">
         <v>3</v>
       </c>
@@ -18859,21 +18903,21 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>2025-03-04 10:30:00-05:00</t>
+          <t>2025-03-04 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>RCM/TIPP Economic Optimism IndexMAR</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr"/>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="F822" t="n">
         <v>3</v>
       </c>
@@ -18881,19 +18925,23 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>2025-03-04 16:30:00-05:00</t>
+          <t>2025-03-04 10:30:00-05:00</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
-      <c r="D823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E823" t="inlineStr"/>
       <c r="F823" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="824">
@@ -18904,7 +18952,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/28</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
@@ -18917,19 +18965,19 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>2025-03-05 07:00:00-05:00</t>
+          <t>2025-03-04 16:30:00-05:00</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>API Crude Oil Stock ChangeFEB/28</t>
         </is>
       </c>
       <c r="C825" t="inlineStr"/>
       <c r="D825" t="inlineStr"/>
       <c r="E825" t="inlineStr"/>
       <c r="F825" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="826">
@@ -18940,7 +18988,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
@@ -18958,14 +19006,14 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C827" t="inlineStr"/>
       <c r="D827" t="inlineStr"/>
       <c r="E827" t="inlineStr"/>
       <c r="F827" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="828">
@@ -18976,7 +19024,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C828" t="inlineStr"/>
@@ -18994,7 +19042,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -19007,12 +19055,12 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>2025-03-05 08:15:00-05:00</t>
+          <t>2025-03-05 07:00:00-05:00</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>ADP Employment ChangeFEB</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -19025,12 +19073,12 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>2025-03-05 09:45:00-05:00</t>
+          <t>2025-03-05 08:15:00-05:00</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>ADP Employment ChangeFEB</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -19048,7 +19096,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -19061,19 +19109,19 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2025-03-05 10:00:00-05:00</t>
+          <t>2025-03-05 09:45:00-05:00</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
       <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr"/>
       <c r="F833" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="834">
@@ -19084,14 +19132,14 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C834" t="inlineStr"/>
       <c r="D834" t="inlineStr"/>
       <c r="E834" t="inlineStr"/>
       <c r="F834" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="835">
@@ -19102,14 +19150,14 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C835" t="inlineStr"/>
       <c r="D835" t="inlineStr"/>
       <c r="E835" t="inlineStr"/>
       <c r="F835" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="836">
@@ -19120,7 +19168,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C836" t="inlineStr"/>
@@ -19138,7 +19186,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C837" t="inlineStr"/>
@@ -19156,14 +19204,14 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C838" t="inlineStr"/>
       <c r="D838" t="inlineStr"/>
       <c r="E838" t="inlineStr"/>
       <c r="F838" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="839">
@@ -19174,25 +19222,25 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C839" t="inlineStr"/>
       <c r="D839" t="inlineStr"/>
       <c r="E839" t="inlineStr"/>
       <c r="F839" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>2025-03-05 10:30:00-05:00</t>
+          <t>2025-03-05 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
@@ -19210,7 +19258,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
@@ -19228,7 +19276,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -19246,7 +19294,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
@@ -19264,14 +19312,14 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr"/>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="845">
@@ -19282,7 +19330,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19300,14 +19348,14 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
       <c r="D846" t="inlineStr"/>
       <c r="E846" t="inlineStr"/>
       <c r="F846" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="847">
@@ -19318,7 +19366,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
@@ -19336,7 +19384,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C848" t="inlineStr"/>
@@ -19349,12 +19397,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2025-03-05 14:00:00-05:00</t>
+          <t>2025-03-05 10:30:00-05:00</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C849" t="inlineStr"/>
@@ -19372,7 +19420,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Fed Beige Book</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C850" t="inlineStr"/>
@@ -19385,12 +19433,12 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2025-03-06 07:30:00-05:00</t>
+          <t>2025-03-05 14:00:00-05:00</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Challenger Job CutsFEB</t>
+          <t>Fed Beige Book</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -19403,19 +19451,19 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2025-03-06 08:30:00-05:00</t>
+          <t>2025-03-06 07:30:00-05:00</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Challenger Job CutsFEB</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="inlineStr"/>
       <c r="E852" t="inlineStr"/>
       <c r="F852" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="853">
@@ -19426,14 +19474,18 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C853" t="inlineStr"/>
       <c r="D853" t="inlineStr"/>
-      <c r="E853" t="inlineStr"/>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F853" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="854">
@@ -19444,14 +19496,14 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C854" t="inlineStr"/>
       <c r="D854" t="inlineStr"/>
       <c r="E854" t="inlineStr"/>
       <c r="F854" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="855">
@@ -19462,20 +19514,12 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C855" t="inlineStr"/>
-      <c r="D855" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E855" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D855" t="inlineStr"/>
+      <c r="E855" t="inlineStr"/>
       <c r="F855" t="n">
         <v>3</v>
       </c>
@@ -19506,14 +19550,14 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr"/>
       <c r="E857" t="inlineStr"/>
       <c r="F857" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="858">
@@ -19524,14 +19568,14 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
       <c r="D858" t="inlineStr"/>
       <c r="E858" t="inlineStr"/>
       <c r="F858" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="859">
@@ -19542,34 +19586,38 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
       <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2025-03-06 10:00:00-05:00</t>
+          <t>2025-03-06 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMJAN</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
-      <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="F860" t="n">
         <v>3</v>
       </c>
@@ -19577,12 +19625,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2025-03-06 10:30:00-05:00</t>
+          <t>2025-03-06 10:00:00-05:00</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/28</t>
+          <t>Wholesale Inventories MoMJAN</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19595,12 +19643,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2025-03-06 12:00:00-05:00</t>
+          <t>2025-03-06 10:30:00-05:00</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -19631,12 +19679,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2025-03-06 16:30:00-05:00</t>
+          <t>2025-03-06 12:00:00-05:00</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Fed Balance SheetMAR/05</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
@@ -19649,19 +19697,19 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2025-03-07 08:30:00-05:00</t>
+          <t>2025-03-06 16:30:00-05:00</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Fed Balance SheetMAR/05</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="866">
@@ -19672,14 +19720,14 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
       <c r="D866" t="inlineStr"/>
       <c r="E866" t="inlineStr"/>
       <c r="F866" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="867">
@@ -19690,16 +19738,12 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
       <c r="D867" t="inlineStr"/>
-      <c r="E867" t="inlineStr">
-        <is>
-          <t>62.6%</t>
-        </is>
-      </c>
+      <c r="E867" t="inlineStr"/>
       <c r="F867" t="n">
         <v>2</v>
       </c>
@@ -19712,14 +19756,18 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr"/>
-      <c r="E868" t="inlineStr"/>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>62.6%</t>
+        </is>
+      </c>
       <c r="F868" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="869">
@@ -19730,14 +19778,14 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr"/>
       <c r="E869" t="inlineStr"/>
       <c r="F869" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="870">
@@ -19748,14 +19796,14 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Government PayrollsFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>
       <c r="D870" t="inlineStr"/>
       <c r="E870" t="inlineStr"/>
       <c r="F870" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="871">
@@ -19766,16 +19814,12 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Government PayrollsFEB</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>7.6%</t>
-        </is>
-      </c>
+      <c r="E871" t="inlineStr"/>
       <c r="F871" t="n">
         <v>3</v>
       </c>
@@ -19788,14 +19832,14 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Average Weekly HoursFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr"/>
       <c r="E872" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F872" t="n">
@@ -19810,12 +19854,16 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsFEB</t>
+          <t>Average Weekly HoursFEB</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr"/>
-      <c r="E873" t="inlineStr"/>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
+      </c>
       <c r="F873" t="n">
         <v>3</v>
       </c>
@@ -19828,7 +19876,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateFEB</t>
+          <t>Manufacturing PayrollsFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
@@ -19841,12 +19889,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2025-03-07 13:00:00-05:00</t>
+          <t>2025-03-07 08:30:00-05:00</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountMAR/07</t>
+          <t>Nonfarm Payrolls PrivateFEB</t>
         </is>
       </c>
       <c r="C875" t="inlineStr"/>
@@ -19864,7 +19912,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountMAR/07</t>
+          <t>Baker Hughes Oil Rig CountMAR/07</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
@@ -19877,12 +19925,12 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2025-03-07 15:00:00-05:00</t>
+          <t>2025-03-07 13:00:00-05:00</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Baker Hughes Total Rigs CountMAR/07</t>
         </is>
       </c>
       <c r="C877" t="inlineStr"/>
@@ -19900,7 +19948,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C878" t="inlineStr"/>
@@ -19928,6 +19976,24 @@
         <v>3</v>
       </c>
     </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2025-03-07 15:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Used Car Prices MoMFEB</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr"/>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +742,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,22 +764,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,15 +786,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3</v>
@@ -816,12 +812,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -838,22 +834,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -864,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -886,18 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,26 +1686,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2098,24 +2098,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
         <v>2</v>
       </c>
@@ -2128,18 +2116,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2154,26 +2146,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2184,22 +2176,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>16.5M</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2214,14 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>Continuing Jobless ClaimsDEC/28</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1848K</t>
+        </is>
+      </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2306,18 +2306,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2328,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2354,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2420,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,22 +2450,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2860,26 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -2890,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2920,18 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2976,18 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,26 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3036,18 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3062,22 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3092,22 +3092,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3122,18 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3282,10 +3282,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3300,12 +3304,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3344,14 +3348,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3592,18 +3592,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,18 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,26 +3678,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3712,14 +3716,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3988,18 +3988,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4252,22 +4252,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,19 +4296,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
         <v>3</v>
@@ -4326,12 +4318,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4348,18 +4340,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4370,15 +4366,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
         <v>3</v>
@@ -4392,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,22 +4440,18 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -4556,18 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -4578,18 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4600,22 +4616,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -4630,16 +4646,20 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F173" t="n">
         <v>3</v>
       </c>
@@ -4652,26 +4672,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4682,22 +4702,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4708,16 +4732,20 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4730,26 +4758,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -4760,24 +4788,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4790,12 +4810,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -4812,22 +4832,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -4842,22 +4858,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4868,26 +4888,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4898,26 +4910,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4928,20 +4940,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4954,26 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5560,22 +5560,18 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -5586,18 +5582,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,22 +6172,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,19 +6194,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6228,12 +6216,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6250,12 +6238,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6272,18 +6260,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6294,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6308,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,15 +6330,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,18 +6356,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,18 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6474,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6504,22 +6508,18 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6870,18 +6870,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6896,22 +6900,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -7178,18 +7178,22 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7204,18 +7208,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7230,22 +7234,26 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -7256,26 +7264,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7286,22 +7290,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,15 +7856,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7908,19 +7904,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,12 +7952,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,18 +7974,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8070,18 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,26 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8126,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,22 +8152,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8186,22 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8212,12 +8208,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8231,7 +8227,7 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8242,22 +8238,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8268,26 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8298,18 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8516,26 +8516,26 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -8546,22 +8546,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8576,20 +8576,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
         <v>2</v>
       </c>
@@ -8602,26 +8594,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -8632,18 +8624,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8658,26 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8684,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -8718,22 +8710,18 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8748,26 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8778,14 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+          <t>Personal Spending MoMDEC</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8904,26 +8904,22 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -8934,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9206,18 +9206,18 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,22 +9258,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9590,22 +9590,18 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F369" t="n">
@@ -9620,22 +9616,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -9646,14 +9634,26 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9664,18 +9664,18 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -9902,19 +9902,15 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="n">
         <v>3</v>
@@ -9928,12 +9924,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,22 +9946,18 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -9976,12 +9968,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,18 +9990,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10020,18 +10016,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10042,22 +10042,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10068,15 +10064,19 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
         <v>3</v>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10196,22 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,26 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -10256,22 +10256,18 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1886K</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -10286,22 +10282,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -10316,22 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>170K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10596,22 +10596,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10626,18 +10626,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10652,22 +10656,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -10678,22 +10682,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>3K</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>-2K</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,18 +10708,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>141K</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10734,26 +10738,26 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10764,26 +10768,26 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -10794,26 +10798,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
@@ -11564,22 +11564,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11616,22 +11616,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11642,18 +11638,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -11664,22 +11664,22 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -11690,18 +11690,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467">
@@ -11976,14 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,18 +12002,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -12020,18 +12028,14 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12046,22 +12050,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12072,22 +12072,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12098,14 +12094,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12120,18 +12116,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -12142,14 +12142,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12164,22 +12168,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -12360,18 +12360,22 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -12382,22 +12386,22 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12408,14 +12412,14 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F492" t="n">
@@ -12430,22 +12434,18 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -12456,18 +12456,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -12478,18 +12478,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12500,18 +12504,22 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
@@ -12522,22 +12530,18 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -12548,18 +12552,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F498" t="n">
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,14 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,18 +12626,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12648,18 +12648,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -12670,18 +12674,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13025,7 +13025,11 @@
           <t>6-Month Bill Auction</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr"/>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>4.220%</t>
+        </is>
+      </c>
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr"/>
       <c r="F519" t="n">
@@ -13043,7 +13047,11 @@
           <t>3-Month Bill Auction</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr"/>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>4.225%</t>
+        </is>
+      </c>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="n">
@@ -13260,14 +13268,18 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13278,18 +13290,14 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13480,18 +13488,22 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F544" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -13624,14 +13636,14 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F550" t="n">
@@ -13646,22 +13658,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+      <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -13932,7 +13940,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13976,7 +13984,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -13994,22 +14002,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D569" t="inlineStr"/>
+      <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -14038,16 +14038,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
         <v>3</v>
       </c>
@@ -14060,18 +14056,14 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F572" t="n">
@@ -14086,22 +14078,22 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -14112,14 +14104,22 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
-      <c r="E574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F574" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575">
@@ -14130,14 +14130,22 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -14508,7 +14516,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -14544,7 +14552,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
@@ -14562,7 +14570,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
@@ -14580,7 +14588,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
@@ -14598,7 +14606,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -14616,7 +14624,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -14670,14 +14678,14 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr"/>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -14868,14 +14876,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14886,7 +14894,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -15250,18 +15258,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -15276,18 +15284,18 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -15402,22 +15410,22 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.13M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="640">
@@ -15506,18 +15514,22 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -15528,22 +15540,22 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>4.13M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F644" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -15580,22 +15592,18 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D646" t="inlineStr"/>
       <c r="E646" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
@@ -15660,7 +15668,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15696,7 +15704,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -15759,7 +15767,11 @@
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr"/>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F655" t="n">
         <v>2</v>
       </c>
@@ -15961,7 +15973,11 @@
       </c>
       <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr"/>
-      <c r="E666" t="inlineStr"/>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F666" t="n">
         <v>3</v>
       </c>
@@ -15997,7 +16013,11 @@
       </c>
       <c r="C668" t="inlineStr"/>
       <c r="D668" t="inlineStr"/>
-      <c r="E668" t="inlineStr"/>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>434.3</t>
+        </is>
+      </c>
       <c r="F668" t="n">
         <v>3</v>
       </c>
@@ -16010,14 +16030,18 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
       <c r="D669" t="inlineStr"/>
-      <c r="E669" t="inlineStr"/>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F669" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="670">
@@ -16028,7 +16052,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -16046,18 +16070,14 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E671" t="inlineStr"/>
       <c r="F671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672">
@@ -16210,14 +16230,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -16228,7 +16248,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -16246,7 +16266,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -16264,14 +16284,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16326,7 +16346,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -16344,7 +16364,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16470,7 +16490,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16524,7 +16544,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -16614,7 +16634,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C701" t="inlineStr"/>
@@ -16632,7 +16652,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C702" t="inlineStr"/>
@@ -16686,7 +16706,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16758,7 +16778,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16794,14 +16814,14 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
       <c r="F711" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="712">
@@ -16812,7 +16832,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C712" t="inlineStr"/>
@@ -16830,7 +16850,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
@@ -16848,7 +16868,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
@@ -16884,7 +16904,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C716" t="inlineStr"/>
@@ -16902,7 +16922,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C717" t="inlineStr"/>
@@ -16920,7 +16940,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C718" t="inlineStr"/>
@@ -16938,14 +16958,14 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
       <c r="F719" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="720">
@@ -17136,7 +17156,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -17154,7 +17174,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17262,7 +17282,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -17352,7 +17372,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -17370,7 +17390,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -17388,7 +17408,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -17406,14 +17426,14 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr"/>
       <c r="F745" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="746">
@@ -17424,22 +17444,22 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="747">
@@ -17450,18 +17470,14 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
       <c r="D747" t="inlineStr"/>
-      <c r="E747" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E747" t="inlineStr"/>
       <c r="F747" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="748">
@@ -17472,14 +17488,14 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="749">
@@ -17490,14 +17506,14 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr"/>
       <c r="F749" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="750">
@@ -17508,14 +17524,22 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr"/>
-      <c r="E750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F750" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="751">
@@ -17526,16 +17550,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
       <c r="D751" t="inlineStr"/>
-      <c r="E751" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="E751" t="inlineStr"/>
       <c r="F751" t="n">
         <v>3</v>
       </c>
@@ -17548,22 +17568,18 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="753">
@@ -17574,7 +17590,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
@@ -17592,18 +17608,14 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F754" t="n">
@@ -17644,14 +17656,22 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
-      <c r="D756" t="inlineStr"/>
-      <c r="E756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F756" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757">
@@ -17888,14 +17908,22 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
-      <c r="D768" t="inlineStr"/>
-      <c r="E768" t="inlineStr"/>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F768" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="769">
@@ -17928,22 +17956,14 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E770" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
       <c r="F770" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="771">
@@ -18128,7 +18148,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18146,12 +18166,16 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
       <c r="D781" t="inlineStr"/>
-      <c r="E781" t="inlineStr"/>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F781" t="n">
         <v>3</v>
       </c>
@@ -18222,7 +18246,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -18240,7 +18264,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
@@ -18276,7 +18300,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18294,7 +18318,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
@@ -18366,14 +18390,14 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr"/>
       <c r="F793" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="794">
@@ -18389,7 +18413,11 @@
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr"/>
-      <c r="E794" t="inlineStr"/>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F794" t="n">
         <v>2</v>
       </c>
@@ -18407,7 +18435,11 @@
       </c>
       <c r="C795" t="inlineStr"/>
       <c r="D795" t="inlineStr"/>
-      <c r="E795" t="inlineStr"/>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F795" t="n">
         <v>1</v>
       </c>
@@ -18447,7 +18479,11 @@
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr"/>
-      <c r="E797" t="inlineStr"/>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F797" t="n">
         <v>1</v>
       </c>
@@ -18522,14 +18558,14 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="802">
@@ -18545,7 +18581,11 @@
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr"/>
-      <c r="E802" t="inlineStr"/>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F802" t="n">
         <v>2</v>
       </c>
@@ -18558,14 +18598,14 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="804">
@@ -18576,7 +18616,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -18616,14 +18656,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -18634,14 +18674,14 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
       <c r="E807" t="inlineStr"/>
       <c r="F807" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="808">
@@ -18652,7 +18692,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
@@ -18675,7 +18715,11 @@
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
-      <c r="E809" t="inlineStr"/>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F809" t="n">
         <v>2</v>
       </c>
@@ -18693,7 +18737,11 @@
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr"/>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="F810" t="n">
         <v>3</v>
       </c>
@@ -18711,7 +18759,11 @@
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
-      <c r="E811" t="inlineStr"/>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="F811" t="n">
         <v>2</v>
       </c>
@@ -18796,18 +18848,14 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
       <c r="D816" t="inlineStr"/>
-      <c r="E816" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E816" t="inlineStr"/>
       <c r="F816" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="817">
@@ -18818,7 +18866,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -18836,14 +18884,14 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
       <c r="D818" t="inlineStr"/>
       <c r="E818" t="inlineStr"/>
       <c r="F818" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="819">
@@ -18854,14 +18902,18 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F819" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="820">
@@ -18872,14 +18924,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -18988,14 +19040,14 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
       <c r="D826" t="inlineStr"/>
       <c r="E826" t="inlineStr"/>
       <c r="F826" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="827">
@@ -19006,7 +19058,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C827" t="inlineStr"/>
@@ -19024,7 +19076,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C828" t="inlineStr"/>
@@ -19042,7 +19094,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -19060,14 +19112,14 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
       <c r="D830" t="inlineStr"/>
       <c r="E830" t="inlineStr"/>
       <c r="F830" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="831">
@@ -19258,7 +19310,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
@@ -19276,7 +19328,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -19294,7 +19346,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
@@ -19474,14 +19526,18 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C853" t="inlineStr"/>
-      <c r="D853" t="inlineStr"/>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F853" t="n">
@@ -19496,7 +19552,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C854" t="inlineStr"/>
@@ -19514,7 +19570,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C855" t="inlineStr"/>
@@ -19532,7 +19588,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
@@ -19550,7 +19606,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -19568,7 +19624,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19586,14 +19642,18 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
       <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr"/>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F859" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="860">
@@ -19604,22 +19664,14 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
-      <c r="D860" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E860" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
       <c r="F860" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="861">
@@ -19666,7 +19718,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
@@ -19684,7 +19736,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
@@ -19966,7 +20018,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
@@ -19984,7 +20036,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C880" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,22 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,22 +768,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,12 +790,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -816,12 +812,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -838,18 +834,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -860,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,15 +882,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>3</v>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,26 +1686,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1798,26 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2002,18 +2002,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2350,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2398,15 +2398,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2420,22 +2424,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,26 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2890,18 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2916,26 +2920,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,7 +3204,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3211,7 +3215,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,26 +3230,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,18 +3562,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3626,14 +3626,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,22 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,15 +4252,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4274,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4296,22 +4300,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4322,22 +4322,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,18 +4366,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4392,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,19 +4440,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -4586,26 +4586,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4616,16 +4608,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4638,16 +4638,24 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F173" t="n">
         <v>3</v>
       </c>
@@ -4660,18 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4682,18 +4698,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4704,26 +4728,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4734,18 +4754,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4760,26 +4780,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4790,18 +4810,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4816,26 +4836,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4846,26 +4866,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4876,26 +4888,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,26 +4910,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4936,24 +4940,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4966,18 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4988,20 +4992,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5352,26 +5352,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -5382,18 +5382,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,22 +5408,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,18 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5972,26 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,18 +6172,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6194,22 +6198,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6220,19 +6220,15 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>3</v>
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,15 +6286,19 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6312,18 +6312,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,22 +6360,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,22 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6560,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6620,22 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6684,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,18 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,18 +7346,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,26 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7398,26 +7398,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7616,18 +7616,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -7638,18 +7638,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,15 +7856,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7904,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,18 +7952,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,26 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -8100,26 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8130,22 +8126,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8160,26 +8152,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8190,18 +8178,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8216,22 +8208,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8242,18 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,18 +8268,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -8826,15 +8826,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8848,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -12002,14 +12002,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,22 +12028,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12050,14 +12050,14 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12072,22 +12072,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12098,14 +12094,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12120,22 +12116,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -12146,14 +12142,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12168,14 +12164,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -12574,22 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,14 +12596,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12648,18 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,14 +12670,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13442,14 +13442,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -13460,14 +13460,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13966,14 +13966,22 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr"/>
-      <c r="E567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F567" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -14156,18 +14164,18 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14182,22 +14190,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E577" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" t="inlineStr"/>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -14208,12 +14208,20 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14226,12 +14234,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14280,16 +14292,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14302,20 +14310,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14758,14 +14758,14 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="608">
@@ -14776,14 +14776,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="609">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14902,14 +14902,14 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="616">
@@ -14920,14 +14920,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -15210,14 +15210,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15258,18 +15262,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -16078,18 +16078,14 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E671" t="inlineStr"/>
       <c r="F671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672">
@@ -16122,18 +16118,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -16144,12 +16140,16 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
         <v>3</v>
       </c>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -16586,14 +16586,14 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="698">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16640,14 +16640,14 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="701">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17694,14 +17694,18 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -17990,18 +17994,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18168,12 +18168,16 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
       <c r="D780" t="inlineStr"/>
-      <c r="E780" t="inlineStr"/>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F780" t="n">
         <v>3</v>
       </c>
@@ -18230,7 +18234,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18324,7 +18328,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18378,7 +18382,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18648,18 +18652,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805">
@@ -18670,12 +18674,16 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr"/>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18688,14 +18696,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -18706,14 +18714,18 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr"/>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F807" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="808">
@@ -18724,18 +18736,14 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="809">
@@ -18746,14 +18754,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="810">
@@ -18764,16 +18772,12 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E810" t="inlineStr"/>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18786,18 +18790,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
@@ -18938,14 +18942,18 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F819" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="820">
@@ -18956,18 +18964,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -18978,7 +18982,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -18996,14 +19000,14 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
       <c r="E822" t="inlineStr"/>
       <c r="F822" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="823">
@@ -19014,7 +19018,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19130,7 +19134,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -19148,7 +19152,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -19166,14 +19170,14 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
       <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr"/>
       <c r="F831" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="832">
@@ -19184,7 +19188,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -19202,14 +19206,14 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
       <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr"/>
       <c r="F833" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="834">
@@ -19400,7 +19404,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19418,7 +19422,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19436,7 +19440,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19616,7 +19620,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
@@ -19634,7 +19638,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -19652,7 +19656,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19670,14 +19674,18 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F859" t="n">
@@ -19692,22 +19700,14 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
-      <c r="D860" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E860" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
       <c r="F860" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="861">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -19754,14 +19754,18 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
       <c r="D863" t="inlineStr"/>
-      <c r="E863" t="inlineStr"/>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F863" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="864">
@@ -19808,7 +19812,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19826,7 +19830,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20108,7 +20112,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20126,7 +20130,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,15 +742,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>3</v>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -860,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,22 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1092,26 +1092,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1122,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1686,26 +1686,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,22 +1746,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1772,26 +1776,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,18 +2046,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,22 +2350,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2376,15 +2372,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2398,22 +2398,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2424,18 +2424,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,22 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,26 +2890,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2920,18 +2920,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -2946,26 +2950,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3036,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,22 +3200,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3267,7 +3267,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3562,22 +3562,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3588,26 +3592,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,18 +3622,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3674,12 +3678,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3693,7 +3697,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3712,14 +3716,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,19 +4252,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,18 +4296,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4322,18 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4344,15 +4348,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4366,22 +4374,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4392,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,18 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4608,24 +4616,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4638,26 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4668,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4690,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,20 +4712,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4754,18 +4734,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4780,26 +4760,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -4810,18 +4790,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4836,26 +4816,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4866,16 +4838,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4888,16 +4868,24 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4910,26 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4940,18 +4928,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,26 +4958,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4992,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5352,26 +5352,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
@@ -5382,18 +5382,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,18 +5412,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,18 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5968,26 +5972,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,22 +6172,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6194,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,18 +6216,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,15 +6264,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6286,19 +6290,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6312,22 +6312,18 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -6338,18 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6624,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6654,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6684,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6714,22 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,26 +7316,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7346,18 +7346,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,18 +7376,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7398,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7616,18 +7616,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,18 +7682,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7856,19 +7864,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7926,22 +7934,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7952,22 +7956,18 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,26 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8126,18 +8130,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,22 +8156,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8178,26 +8186,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8208,26 +8216,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8238,22 +8242,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,18 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8298,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8826,19 +8826,15 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8852,15 +8848,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -12002,22 +12002,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -12028,14 +12028,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12050,14 +12054,14 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12072,14 +12076,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12094,14 +12098,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12116,22 +12120,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -12142,14 +12142,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12164,22 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12190,22 +12194,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482">
@@ -12574,14 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,18 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,22 +12622,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12648,14 +12644,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13279,7 +13279,11 @@
           <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr"/>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>$87.1B</t>
+        </is>
+      </c>
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="n">
@@ -13297,7 +13301,11 @@
           <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>$72B</t>
+        </is>
+      </c>
       <c r="D533" t="inlineStr">
         <is>
           <t>$149.1B</t>
@@ -13319,7 +13327,11 @@
           <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr"/>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>$-49.7B</t>
+        </is>
+      </c>
       <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
@@ -13352,14 +13364,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13442,7 +13454,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13460,14 +13472,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="543">
@@ -13478,7 +13490,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13966,18 +13978,18 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F567" t="n">
@@ -14164,22 +14176,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="577">
@@ -14190,7 +14194,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14208,20 +14212,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14234,16 +14230,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14292,12 +14284,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14310,12 +14306,20 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14328,14 +14332,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F584" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="585">
@@ -14740,7 +14752,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14758,7 +14770,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14776,7 +14788,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14794,14 +14806,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="610">
@@ -14812,14 +14824,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14830,7 +14842,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14866,7 +14878,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14884,7 +14896,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14902,14 +14914,14 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
@@ -14920,14 +14932,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617">
@@ -14938,7 +14950,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -15210,18 +15222,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15262,14 +15270,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16060,7 +16072,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -16078,7 +16090,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16118,18 +16130,14 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674">
@@ -16140,18 +16148,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16162,12 +16170,16 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr"/>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F675" t="n">
         <v>3</v>
       </c>
@@ -16586,14 +16598,14 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="698">
@@ -16604,14 +16616,14 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="699">
@@ -16622,7 +16634,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16640,7 +16652,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16730,7 +16742,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16784,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16802,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16820,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16838,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17000,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17018,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17198,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17216,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17694,18 +17706,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -17994,14 +18002,18 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18168,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18234,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18328,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18382,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18652,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="805">
@@ -18674,16 +18686,12 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E805" t="inlineStr"/>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18696,14 +18704,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="807">
@@ -18714,18 +18722,14 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E807" t="inlineStr"/>
       <c r="F807" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="808">
@@ -18736,14 +18740,18 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr"/>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F808" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809">
@@ -18754,14 +18762,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="810">
@@ -18772,12 +18780,16 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr"/>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18790,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="812">
@@ -18942,18 +18954,14 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E819" t="inlineStr"/>
       <c r="F819" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="820">
@@ -18964,14 +18972,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="821">
@@ -18982,7 +18990,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19000,14 +19008,18 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
-      <c r="E822" t="inlineStr"/>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F822" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="823">
@@ -19018,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19134,14 +19146,14 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
       <c r="D829" t="inlineStr"/>
       <c r="E829" t="inlineStr"/>
       <c r="F829" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="830">
@@ -19152,7 +19164,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -19170,7 +19182,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -19188,7 +19200,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -19206,14 +19218,14 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
       <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr"/>
       <c r="F833" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="834">
@@ -19404,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19422,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19440,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19620,14 +19632,18 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
       <c r="D856" t="inlineStr"/>
-      <c r="E856" t="inlineStr"/>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F856" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="857">
@@ -19638,7 +19654,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -19656,7 +19672,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19674,22 +19690,14 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="860">
@@ -19700,7 +19708,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -19718,7 +19726,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19736,7 +19744,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -19754,14 +19762,18 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
-      <c r="D863" t="inlineStr"/>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F863" t="n">
@@ -19812,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19830,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20112,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20130,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,22 +742,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +790,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,18 +812,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -838,12 +838,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,15 +860,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>3</v>
@@ -882,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,26 +1746,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1776,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2002,18 +2002,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,18 +2046,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2350,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,22 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,22 +2402,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2424,22 +2424,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2450,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2472,15 +2468,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,26 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -2890,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2920,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2950,18 +2946,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -2976,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3036,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3159,7 +3159,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,26 +3200,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3540,14 +3540,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3562,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3581,7 +3577,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3592,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3622,22 +3618,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3708,18 +3708,18 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4296,22 +4296,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4322,22 +4318,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,19 +4340,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4374,18 +4362,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4396,18 +4388,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4414,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,15 +4436,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4556,26 +4556,18 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,26 +4578,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4616,18 +4604,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,16 +4664,24 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4690,16 +4694,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4712,18 +4724,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4734,18 +4754,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4760,26 +4780,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4790,18 +4810,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4816,18 +4836,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4838,24 +4866,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,26 +4888,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4898,26 +4918,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -4928,26 +4948,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4958,20 +4970,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
         <v>3</v>
       </c>
@@ -4984,26 +4992,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5352,22 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5382,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5412,18 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,26 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -5972,18 +5972,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -5998,26 +6002,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,18 +6194,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6216,22 +6220,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6242,15 +6242,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6264,19 +6268,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6290,18 +6290,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -6564,22 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6620,22 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7346,26 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -7376,18 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,18 +7402,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,18 +7594,18 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,18 +7682,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,15 +7856,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7904,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,18 +7952,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,22 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8100,26 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8130,18 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,26 +8152,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8186,26 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8216,22 +8208,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8242,18 +8238,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8298,18 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8826,15 +8826,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8848,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -11976,22 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -12002,22 +11998,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -12028,22 +12020,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -12054,14 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12076,14 +12072,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12098,14 +12094,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12120,14 +12116,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,22 +12142,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -12168,22 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12600,14 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,14 +12626,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12644,18 +12652,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12674,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13364,14 +13364,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -13978,22 +13978,14 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="568">
@@ -14176,7 +14168,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14194,14 +14186,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14212,12 +14212,20 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14230,12 +14238,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14284,16 +14296,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14306,20 +14314,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14332,18 +14332,18 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F584" t="n">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14824,14 +14824,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="611">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14878,14 +14878,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14896,14 +14896,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -15222,14 +15222,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15270,18 +15274,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16072,12 +16072,16 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F670" t="n">
         <v>3</v>
       </c>
@@ -16090,7 +16094,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16130,7 +16134,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16148,18 +16152,14 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E674" t="inlineStr"/>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -16170,18 +16170,18 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
       <c r="E675" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F675" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="676">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16616,14 +16616,14 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="699">
@@ -16634,14 +16634,14 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="700">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17706,14 +17706,18 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -18002,18 +18006,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18664,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805">
@@ -18686,12 +18686,16 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr"/>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18704,14 +18708,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -18722,14 +18726,18 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr"/>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F807" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="808">
@@ -18740,18 +18748,14 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="809">
@@ -18762,14 +18766,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="810">
@@ -18780,16 +18784,12 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E810" t="inlineStr"/>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18802,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
@@ -18954,14 +18954,14 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="820">
@@ -18972,14 +18972,18 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr"/>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F820" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="821">
@@ -18990,7 +18994,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19008,18 +19012,14 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E822" t="inlineStr"/>
       <c r="F822" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="823">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19146,14 +19146,14 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
       <c r="D829" t="inlineStr"/>
       <c r="E829" t="inlineStr"/>
       <c r="F829" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="830">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -19200,14 +19200,14 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
       <c r="D832" t="inlineStr"/>
       <c r="E832" t="inlineStr"/>
       <c r="F832" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="833">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19632,14 +19632,18 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
-      <c r="D856" t="inlineStr"/>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F856" t="n">
@@ -19654,7 +19658,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -19672,7 +19676,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19690,7 +19694,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
@@ -19708,7 +19712,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -19726,7 +19730,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19744,14 +19748,18 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr"/>
-      <c r="E862" t="inlineStr"/>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F862" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="863">
@@ -19762,22 +19770,14 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
-      <c r="D863" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E863" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D863" t="inlineStr"/>
+      <c r="E863" t="inlineStr"/>
       <c r="F863" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="864">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,22 +742,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -768,15 +764,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>3</v>
@@ -790,12 +790,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -812,22 +812,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -838,12 +834,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,22 +856,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,18 +904,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1092,26 +1092,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1122,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1798,26 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2002,18 +2002,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,22 +2350,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2376,22 +2372,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,15 +2394,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2424,18 +2420,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,22 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2886,26 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2976,18 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3002,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3148,22 +3148,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3178,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,7 +3230,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3237,7 +3241,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3532,18 +3532,18 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3558,22 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3686,14 +3686,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3708,22 +3704,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,15 +4252,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4274,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4296,18 +4300,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4318,18 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4340,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4362,22 +4374,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4388,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4414,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,19 +4440,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4556,18 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4578,20 +4586,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
         <v>3</v>
       </c>
@@ -4604,26 +4608,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4634,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4664,26 +4660,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,24 +4690,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4724,26 +4712,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4754,18 +4734,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4780,26 +4760,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4810,18 +4782,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4836,26 +4808,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4866,18 +4834,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4888,26 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4918,26 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4948,16 +4924,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4970,18 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,16 +4984,24 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5438,22 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5468,18 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5972,26 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6194,22 +6194,18 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6220,12 +6216,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,19 +6238,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6268,18 +6260,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6290,22 +6286,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,18 +6308,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6334,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,15 +6378,19 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
         <v>3</v>
@@ -6534,26 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6624,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6654,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,18 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,26 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7402,18 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,18 +7594,18 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7660,18 +7660,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7856,19 +7864,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7926,22 +7934,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7952,22 +7956,18 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,18 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,18 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,26 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8152,22 +8156,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8178,26 +8186,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8208,26 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8238,18 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8264,26 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8826,19 +8826,15 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8852,15 +8848,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467">
@@ -11976,14 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,14 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12020,22 +12024,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -12046,22 +12050,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12072,14 +12076,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12094,14 +12098,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12116,22 +12124,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -12142,22 +12150,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12168,22 +12172,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,22 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,18 +12596,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12626,22 +12618,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12652,14 +12644,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,14 +12670,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13454,14 +13454,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -14168,14 +14168,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F576" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -14186,18 +14194,18 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -14212,20 +14220,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14238,16 +14238,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14296,12 +14292,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14314,12 +14314,20 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14332,22 +14340,14 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E584" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D584" t="inlineStr"/>
+      <c r="E584" t="inlineStr"/>
       <c r="F584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -14752,14 +14752,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14878,14 +14878,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -14896,14 +14896,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -15222,18 +15222,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15274,14 +15270,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16072,18 +16072,18 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F670" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
@@ -16134,12 +16134,16 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F673" t="n">
         <v>3</v>
       </c>
@@ -16152,7 +16156,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -16170,18 +16174,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16634,14 +16634,14 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="700">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16742,14 +16742,14 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17706,18 +17706,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -18006,14 +18002,18 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18664,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="805">
@@ -18686,16 +18686,12 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E805" t="inlineStr"/>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18708,14 +18704,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="807">
@@ -18726,18 +18722,14 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E807" t="inlineStr"/>
       <c r="F807" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="808">
@@ -18748,14 +18740,18 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr"/>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F808" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809">
@@ -18766,14 +18762,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="810">
@@ -18784,12 +18780,16 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr"/>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18802,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="812">
@@ -18954,14 +18954,18 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F819" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="820">
@@ -18972,18 +18976,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19012,14 +19012,14 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
       <c r="E822" t="inlineStr"/>
       <c r="F822" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="823">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -19164,14 +19164,14 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
       <c r="D830" t="inlineStr"/>
       <c r="E830" t="inlineStr"/>
       <c r="F830" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="831">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -19200,14 +19200,14 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
       <c r="D832" t="inlineStr"/>
       <c r="E832" t="inlineStr"/>
       <c r="F832" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="833">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19632,22 +19632,14 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E856" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr"/>
       <c r="F856" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="857">
@@ -19658,14 +19650,18 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr"/>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F857" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="858">
@@ -19676,7 +19672,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19694,7 +19690,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
@@ -19712,7 +19708,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -19730,7 +19726,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19748,14 +19744,18 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
-      <c r="D862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F862" t="n">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,18 +742,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -764,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -786,22 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,15 +816,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -834,22 +842,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -860,12 +864,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1798,26 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2002,18 +2002,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2350,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2398,15 +2398,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2420,22 +2424,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,26 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2890,22 +2890,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2920,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -2946,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3032,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,18 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,22 +3200,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3267,7 +3267,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3562,22 +3562,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3588,26 +3592,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3618,18 +3622,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,12 +3678,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3693,7 +3697,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3712,14 +3716,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,15 +4252,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4274,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4296,22 +4300,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4322,22 +4322,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,12 +4344,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4370,18 +4366,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4392,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4414,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,19 +4440,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4556,18 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4578,16 +4586,24 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F171" t="n">
         <v>3</v>
       </c>
@@ -4600,18 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4622,18 +4646,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4644,26 +4676,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4674,16 +4706,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4696,26 +4736,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4726,18 +4766,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4752,20 +4792,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4778,18 +4814,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4804,26 +4840,18 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4834,24 +4862,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4864,26 +4884,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4894,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4932,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,26 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5352,26 +5352,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
@@ -5382,18 +5382,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,18 +5412,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5464,22 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5972,26 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,15 +6176,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6194,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6216,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6238,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6260,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6282,22 +6294,18 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6308,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6330,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6352,19 +6360,15 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -6564,22 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6620,22 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7346,26 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -7376,18 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,18 +7402,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7616,18 +7616,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,18 +7682,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,15 +7856,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7904,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,18 +7952,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,26 +8070,26 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -8100,18 +8100,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8126,18 +8130,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,26 +8160,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8182,18 +8186,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,22 +8212,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8234,26 +8242,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,22 +8268,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -8826,15 +8826,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8848,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -12002,14 +11998,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,22 +12024,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -12050,14 +12050,14 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12072,22 +12072,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -12098,14 +12094,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12120,14 +12116,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12142,14 +12142,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12164,22 +12164,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -12574,22 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,14 +12596,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12648,18 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,14 +12670,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13364,14 +13364,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -13978,22 +13978,14 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="568">
@@ -14176,7 +14168,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14194,14 +14186,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14212,12 +14212,20 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14230,12 +14238,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14284,16 +14296,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14306,20 +14314,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14332,18 +14332,18 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F584" t="n">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14788,14 +14788,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="609">
@@ -14806,14 +14806,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="610">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="616">
@@ -14932,14 +14932,14 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
       <c r="F616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -15222,14 +15222,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15270,18 +15274,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16072,12 +16072,16 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F670" t="n">
         <v>3</v>
       </c>
@@ -16090,7 +16094,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16130,18 +16134,14 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="674">
@@ -16152,14 +16152,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -16170,16 +16174,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
         <v>3</v>
       </c>
@@ -16598,14 +16598,14 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="698">
@@ -16616,14 +16616,14 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="699">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17706,14 +17706,18 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -18002,18 +18006,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18664,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805">
@@ -18686,12 +18686,16 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr"/>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18704,14 +18708,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -18722,14 +18726,18 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr"/>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F807" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="808">
@@ -18740,18 +18748,14 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="809">
@@ -18762,14 +18766,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="810">
@@ -18780,16 +18784,12 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E810" t="inlineStr"/>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18802,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
@@ -18954,14 +18954,18 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F819" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="820">
@@ -18972,18 +18976,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19012,14 +19012,14 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
       <c r="E822" t="inlineStr"/>
       <c r="F822" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="823">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19146,14 +19146,14 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
       <c r="D829" t="inlineStr"/>
       <c r="E829" t="inlineStr"/>
       <c r="F829" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="830">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -19218,14 +19218,14 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
       <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr"/>
       <c r="F833" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="834">
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
@@ -19650,7 +19650,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19686,14 +19686,18 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F859" t="n">
@@ -19708,22 +19712,14 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
-      <c r="D860" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E860" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
       <c r="F860" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="861">
@@ -19734,7 +19730,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19752,7 +19748,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -19770,14 +19766,18 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
       <c r="D863" t="inlineStr"/>
-      <c r="E863" t="inlineStr"/>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F863" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="864">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,22 +742,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -768,12 +764,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,22 +786,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -816,22 +808,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -842,12 +834,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -864,18 +856,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,15 +904,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>3</v>
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1092,26 +1092,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1122,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1746,22 +1746,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1772,26 +1776,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,18 +2046,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,22 +2350,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2376,15 +2372,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2398,22 +2398,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2424,18 +2424,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,26 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -2890,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2920,22 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3002,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3028,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3062,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3092,18 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3159,7 +3159,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,26 +3200,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,22 +3252,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3540,14 +3540,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3562,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3581,7 +3577,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3592,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3622,22 +3618,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3678,22 +3678,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3708,18 +3708,18 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,19 +4252,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,18 +4296,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4322,18 +4322,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4344,15 +4348,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4366,22 +4374,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4392,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,18 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,26 +4578,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4616,26 +4608,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4646,26 +4630,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4676,26 +4656,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4706,24 +4678,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4736,26 +4700,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4766,18 +4730,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4792,18 +4756,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4814,18 +4786,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4840,16 +4812,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4862,18 +4842,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4884,18 +4872,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,20 +4902,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4932,16 +4924,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4954,26 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5352,22 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5382,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5412,18 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,26 +5438,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5468,18 +5468,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,18 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5968,26 +5972,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,19 +6172,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6202,12 +6194,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6224,12 +6216,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,18 +6238,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -6268,22 +6264,18 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6294,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6308,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,15 +6330,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6360,18 +6356,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,26 +6534,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6624,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6654,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,18 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,26 +7368,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7402,18 +7398,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,18 +7594,18 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,18 +7682,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7856,19 +7864,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7926,22 +7934,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7952,22 +7956,18 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,26 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -8100,26 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -8130,22 +8126,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8160,22 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8186,18 +8182,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8212,26 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8242,18 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,18 +8268,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -8826,19 +8826,15 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8852,15 +8848,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,14 +11842,14 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,14 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -11998,22 +12002,22 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -12024,22 +12028,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -12050,14 +12054,14 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12072,14 +12076,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12094,14 +12098,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12116,22 +12120,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -12142,14 +12146,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12164,22 +12172,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -12190,22 +12194,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="482">
@@ -12574,14 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,18 +12600,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,22 +12622,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12648,14 +12644,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13454,14 +13454,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -14168,14 +14168,22 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F576" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -14186,18 +14194,18 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F577" t="n">
@@ -14212,20 +14220,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14238,16 +14238,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14296,12 +14292,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14314,12 +14314,20 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14332,22 +14340,14 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E584" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D584" t="inlineStr"/>
+      <c r="E584" t="inlineStr"/>
       <c r="F584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14806,14 +14806,14 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14824,14 +14824,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="611">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14896,14 +14896,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
@@ -14914,14 +14914,14 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -15222,18 +15222,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15274,14 +15270,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16072,16 +16072,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
         <v>3</v>
       </c>
@@ -16134,12 +16130,16 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F673" t="n">
         <v>3</v>
       </c>
@@ -16152,18 +16152,14 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E674" t="inlineStr"/>
       <c r="F674" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675">
@@ -16174,14 +16170,18 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr"/>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F675" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="676">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16616,14 +16616,14 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="699">
@@ -16634,14 +16634,14 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="700">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17706,18 +17706,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -18006,14 +18002,18 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18664,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="805">
@@ -18686,16 +18686,12 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E805" t="inlineStr"/>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18708,14 +18704,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="807">
@@ -18726,18 +18722,14 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E807" t="inlineStr"/>
       <c r="F807" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="808">
@@ -18748,14 +18740,18 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr"/>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F808" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809">
@@ -18766,14 +18762,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="810">
@@ -18784,12 +18780,16 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr"/>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18802,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="812">
@@ -18954,18 +18954,14 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E819" t="inlineStr"/>
       <c r="F819" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="820">
@@ -18976,14 +18972,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="821">
@@ -18994,7 +18990,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19012,14 +19008,18 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
-      <c r="E822" t="inlineStr"/>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F822" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="823">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19146,14 +19146,14 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
       <c r="D829" t="inlineStr"/>
       <c r="E829" t="inlineStr"/>
       <c r="F829" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="830">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -19200,14 +19200,14 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
       <c r="D832" t="inlineStr"/>
       <c r="E832" t="inlineStr"/>
       <c r="F832" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="833">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19632,14 +19632,18 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
       <c r="D856" t="inlineStr"/>
-      <c r="E856" t="inlineStr"/>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F856" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="857">
@@ -19650,7 +19654,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -19668,7 +19672,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19686,22 +19690,14 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="860">
@@ -19712,7 +19708,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -19730,7 +19726,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19748,7 +19744,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -19766,14 +19762,18 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
-      <c r="D863" t="inlineStr"/>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F863" t="n">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,15 +720,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>3</v>
@@ -742,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -764,18 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -786,12 +794,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -808,22 +816,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -834,12 +838,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -856,22 +860,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -904,22 +904,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,26 +1686,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,26 +1746,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1776,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,22 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1828,26 +1828,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2002,18 +2002,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,18 +2046,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2350,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,22 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,22 +2402,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2424,22 +2424,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2450,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2472,15 +2468,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,18 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2886,26 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2976,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3088,26 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3148,22 +3148,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3178,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,7 +3230,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3237,7 +3241,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,26 +3256,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3532,18 +3532,18 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -3558,22 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3648,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3686,14 +3686,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3708,22 +3704,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4296,22 +4296,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4322,22 +4318,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4348,19 +4340,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4374,18 +4362,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4396,18 +4388,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4414,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,15 +4436,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4556,16 +4556,24 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>3</v>
       </c>
@@ -4578,26 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4608,16 +4616,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4630,20 +4646,16 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
         <v>3</v>
       </c>
@@ -4656,18 +4668,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4678,18 +4698,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4700,26 +4728,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4730,18 +4758,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4756,26 +4784,18 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -4786,18 +4806,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4812,26 +4832,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4842,26 +4862,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4872,26 +4884,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4902,18 +4910,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4924,24 +4940,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
         <v>3</v>
       </c>
@@ -4954,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4992,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5352,18 +5352,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,26 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5438,22 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5468,18 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,26 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -5972,18 +5972,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -5998,26 +6002,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,18 +6172,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6194,15 +6198,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6216,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6238,22 +6246,18 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -6264,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6330,19 +6334,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
         <v>3</v>
@@ -6356,22 +6356,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6534,22 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
@@ -6560,26 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6620,22 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6654,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6684,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6714,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,18 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7342,18 +7346,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,26 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -7398,26 +7398,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,18 +7594,18 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7660,18 +7660,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,15 +7856,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7904,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,18 +7952,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,18 +8070,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,26 +8100,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8126,18 +8130,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,26 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8182,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -8212,22 +8212,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8238,22 +8242,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,18 +8268,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8298,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8826,15 +8826,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8848,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,14 +11734,14 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,7 +11788,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -12002,22 +12002,18 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -12028,22 +12024,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -12054,14 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F475" t="n">
@@ -12076,14 +12072,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12098,14 +12094,14 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12120,22 +12116,22 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -12146,22 +12142,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -12172,14 +12168,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,22 +12574,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12600,14 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12622,14 +12626,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F501" t="n">
@@ -12644,18 +12652,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12674,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13454,14 +13454,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13978,14 +13978,22 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr"/>
-      <c r="E567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F567" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -14168,18 +14176,18 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F576" t="n">
@@ -14194,22 +14202,14 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E577" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" t="inlineStr"/>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -14220,12 +14220,20 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14238,12 +14246,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14292,16 +14304,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14314,20 +14322,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -14752,14 +14752,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14824,14 +14824,14 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="611">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14878,14 +14878,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14896,14 +14896,14 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -15222,14 +15222,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15270,18 +15274,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16072,14 +16072,18 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F670" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="671">
@@ -16090,7 +16094,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -16130,16 +16134,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
         <v>3</v>
       </c>
@@ -16152,12 +16152,16 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F674" t="n">
         <v>3</v>
       </c>
@@ -16170,18 +16174,14 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16634,14 +16634,14 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
       <c r="D699" t="inlineStr"/>
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="700">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
@@ -16742,14 +16742,14 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="706">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17706,14 +17706,18 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -18002,18 +18006,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18664,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805">
@@ -18686,12 +18686,16 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr"/>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18704,14 +18708,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -18722,14 +18726,18 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr"/>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F807" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="808">
@@ -18740,18 +18748,14 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="809">
@@ -18762,14 +18766,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="810">
@@ -18780,16 +18784,12 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E810" t="inlineStr"/>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18802,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
@@ -18954,14 +18954,14 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="820">
@@ -18972,14 +18972,18 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr"/>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F820" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="821">
@@ -18990,7 +18994,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19008,18 +19012,14 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E822" t="inlineStr"/>
       <c r="F822" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="823">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -19164,14 +19164,14 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
       <c r="D830" t="inlineStr"/>
       <c r="E830" t="inlineStr"/>
       <c r="F830" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="831">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -19200,14 +19200,14 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
       <c r="D832" t="inlineStr"/>
       <c r="E832" t="inlineStr"/>
       <c r="F832" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="833">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19632,14 +19632,18 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
-      <c r="D856" t="inlineStr"/>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F856" t="n">
@@ -19654,7 +19658,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -19672,7 +19676,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19690,7 +19694,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
@@ -19708,7 +19712,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -19726,7 +19730,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19744,14 +19748,18 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr"/>
-      <c r="E862" t="inlineStr"/>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F862" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="863">
@@ -19762,22 +19770,14 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
-      <c r="D863" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E863" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D863" t="inlineStr"/>
+      <c r="E863" t="inlineStr"/>
       <c r="F863" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="864">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,22 +720,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,22 +768,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,12 +790,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -816,12 +812,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -838,18 +834,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -860,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,15 +882,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>3</v>
@@ -904,22 +908,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1092,26 +1092,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1122,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1398,26 +1398,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1428,22 +1424,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1686,26 +1686,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1716,22 +1716,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1746,18 +1746,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,22 +1772,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1798,26 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2002,18 +2002,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,22 +2350,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2376,22 +2372,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,15 +2394,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2424,18 +2420,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,26 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2890,18 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -2916,26 +2920,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2976,22 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3032,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3148,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3178,7 +3174,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3189,7 +3185,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3204,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3230,22 +3226,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3532,22 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3558,7 +3562,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3566,14 +3570,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3618,22 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3678,18 +3678,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,15 +4252,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4274,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4296,18 +4300,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4318,18 +4326,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -4340,12 +4352,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4362,22 +4374,18 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -4388,22 +4396,18 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -4414,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4436,19 +4440,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -4586,26 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -4616,24 +4616,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4646,18 +4638,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4668,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4694,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,26 +4716,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,18 +4738,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4784,16 +4764,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4806,18 +4794,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4832,26 +4820,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -4862,16 +4850,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4884,20 +4880,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4910,26 +4902,18 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4940,18 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4962,26 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5352,18 +5352,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -5378,22 +5382,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -5438,18 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,26 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -5972,26 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6002,18 +5998,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -6150,18 +6150,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -6172,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6198,19 +6198,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6224,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6264,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,15 +6308,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>3</v>
@@ -6334,18 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6356,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6378,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6564,26 +6564,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6594,22 +6590,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6624,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6654,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6684,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6714,22 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,26 +7316,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7346,18 +7346,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7372,18 +7376,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7398,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7616,12 +7616,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7638,18 +7638,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -7660,18 +7660,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7790,18 +7790,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -7812,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7834,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7856,19 +7864,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7904,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7926,22 +7934,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7952,22 +7956,18 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,22 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8100,26 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8130,18 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,22 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8182,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8212,26 +8212,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8242,18 +8238,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,26 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8298,18 +8294,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8826,19 +8826,15 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8852,15 +8848,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9846,26 +9850,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,14 +11510,14 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -11824,14 +11824,14 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,22 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -12002,14 +12002,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,14 +12024,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F474" t="n">
@@ -12046,22 +12050,22 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -12072,14 +12076,14 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12094,14 +12098,18 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F477" t="n">
@@ -12116,22 +12124,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -12142,22 +12146,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -12168,22 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,22 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12600,18 +12596,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12626,22 +12618,22 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -12652,14 +12644,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12674,14 +12670,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F503" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13364,14 +13364,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13472,14 +13472,14 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="543">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13978,18 +13978,18 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F567" t="n">
@@ -14176,22 +14176,14 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="577">
@@ -14202,7 +14194,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -14220,20 +14212,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14246,16 +14230,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14304,12 +14284,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14322,12 +14306,20 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14340,14 +14332,22 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F584" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="585">
@@ -14752,14 +14752,14 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="612">
@@ -14878,14 +14878,14 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14950,14 +14950,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="618">
@@ -15222,18 +15222,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D631" t="inlineStr"/>
       <c r="E631" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15274,14 +15270,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16072,18 +16072,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E670" t="inlineStr"/>
       <c r="F670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="671">
@@ -16094,14 +16090,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr"/>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F671" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="672">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -16152,16 +16152,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E674" t="inlineStr"/>
       <c r="F674" t="n">
         <v>3</v>
       </c>
@@ -16174,12 +16170,16 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr"/>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F675" t="n">
         <v>3</v>
       </c>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16652,14 +16652,14 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="701">
@@ -16742,14 +16742,14 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
       <c r="F705" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="706">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17706,18 +17706,14 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -18006,14 +18002,18 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18664,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="805">
@@ -18686,16 +18686,12 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E805" t="inlineStr"/>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18708,14 +18704,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="807">
@@ -18726,18 +18722,14 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E807" t="inlineStr"/>
       <c r="F807" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="808">
@@ -18748,14 +18740,18 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr"/>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F808" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809">
@@ -18766,14 +18762,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="810">
@@ -18784,12 +18780,16 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr"/>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18802,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="812">
@@ -18954,14 +18954,18 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F819" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="820">
@@ -18972,18 +18976,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19012,14 +19012,14 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
       <c r="E822" t="inlineStr"/>
       <c r="F822" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="823">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -19164,14 +19164,14 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
       <c r="D830" t="inlineStr"/>
       <c r="E830" t="inlineStr"/>
       <c r="F830" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="831">
@@ -19182,14 +19182,14 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
       <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr"/>
       <c r="F831" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="832">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19632,22 +19632,14 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E856" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr"/>
       <c r="F856" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="857">
@@ -19658,14 +19650,18 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr"/>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F857" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="858">
@@ -19676,7 +19672,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19694,7 +19690,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
@@ -19712,7 +19708,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -19730,7 +19726,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19748,14 +19744,18 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
-      <c r="D862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F862" t="n">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,22 +720,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -746,15 +742,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>3</v>
@@ -768,12 +768,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -790,18 +790,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,22 +838,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -860,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,22 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +908,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,22 +1746,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1772,26 +1776,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -1802,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1980,18 +1980,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2046,18 +2046,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,18 +2350,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2372,15 +2376,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2394,22 +2402,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>-0.6M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2420,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,22 +2472,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -2860,22 +2860,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -2890,26 +2890,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2920,18 +2920,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -2946,26 +2950,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +3006,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3036,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3148,18 +3148,18 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,7 +3204,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3211,7 +3215,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,26 +3230,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3562,18 +3562,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3626,14 +3626,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3648,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3678,22 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -3966,18 +3966,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,19 +4252,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
         <v>3</v>
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,22 +4296,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4326,22 +4318,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>0.765M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -4352,15 +4340,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4374,18 +4366,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4396,18 +4392,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,26 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -4586,26 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4616,18 +4616,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4646,18 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,20 +4668,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
         <v>3</v>
       </c>
@@ -4694,16 +4690,24 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
         <v>3</v>
       </c>
@@ -4716,18 +4720,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4738,18 +4750,18 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -4764,26 +4776,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4794,18 +4806,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -4820,26 +4832,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -4850,24 +4862,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4880,18 +4884,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4902,16 +4914,24 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F183" t="n">
         <v>3</v>
       </c>
@@ -4924,26 +4944,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,26 +4966,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4988,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5352,26 +5352,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -5382,18 +5382,18 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -5408,22 +5408,18 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5438,18 +5434,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5464,26 +5464,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5942,18 +5942,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>1899K</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -5968,26 +5972,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5998,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1860K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6150,22 +6150,18 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -6176,12 +6172,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,18 +6194,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6220,15 +6220,19 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>3</v>
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6286,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,19 +6312,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>3</v>
@@ -6334,22 +6334,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,18 +6356,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6534,26 +6534,26 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -6564,22 +6564,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6590,22 +6594,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -6620,22 +6624,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6650,26 +6654,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>4.19M</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -6710,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7316,26 +7316,22 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7346,26 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -7376,18 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,18 +7402,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -7428,18 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7454,18 +7454,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -7616,18 +7616,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -7638,18 +7638,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7790,22 +7790,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,15 +7856,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7886,12 +7882,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7908,19 +7904,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,18 +7952,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,18 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,18 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,26 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8152,26 +8156,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8182,26 +8182,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,22 +8208,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8238,18 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8264,26 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,22 +8298,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8826,15 +8826,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="n">
         <v>3</v>
@@ -8848,19 +8852,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9472,18 +9472,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9516,18 +9516,18 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9768,18 +9768,18 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F376" t="n">
@@ -9794,26 +9794,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -9850,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9876,18 +9876,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F380" t="n">
@@ -10842,12 +10842,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMJAN</t>
+          <t>Used Car Prices YoYJAN</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYJAN</t>
+          <t>Used Car Prices MoMJAN</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -11474,14 +11474,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -11546,14 +11546,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -11752,14 +11752,14 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -11770,14 +11770,14 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -11806,14 +11806,14 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -11976,22 +11976,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -12002,14 +11998,14 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F473" t="n">
@@ -12024,22 +12020,22 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -12050,22 +12046,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -12076,14 +12068,18 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F476" t="n">
@@ -12098,22 +12094,22 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -12124,14 +12120,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F478" t="n">
@@ -12146,14 +12146,14 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F479" t="n">
@@ -12168,22 +12168,22 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -12194,14 +12194,14 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F481" t="n">
@@ -12574,14 +12574,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -12596,14 +12600,18 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F500" t="n">
@@ -12618,22 +12626,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12644,18 +12648,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F502" t="n">
@@ -12670,22 +12670,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -13364,14 +13364,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13490,14 +13490,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -13978,22 +13978,14 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="568">
@@ -14176,7 +14168,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14194,14 +14186,22 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -14212,12 +14212,20 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F578" t="n">
         <v>3</v>
       </c>
@@ -14230,12 +14238,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F579" t="n">
         <v>3</v>
       </c>
@@ -14284,16 +14296,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
         <v>3</v>
       </c>
@@ -14306,20 +14314,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
         <v>3</v>
       </c>
@@ -14332,18 +14332,18 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F584" t="n">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
@@ -14770,14 +14770,14 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="608">
@@ -14788,14 +14788,14 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="609">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14842,14 +14842,14 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr"/>
       <c r="E611" t="inlineStr"/>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="612">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
@@ -14950,14 +14950,14 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -15222,14 +15222,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F631" t="n">
@@ -15270,18 +15274,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -16072,12 +16072,16 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F670" t="n">
         <v>3</v>
       </c>
@@ -16090,18 +16094,14 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E671" t="inlineStr"/>
       <c r="F671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672">
@@ -16134,14 +16134,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -16152,7 +16156,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -16170,16 +16174,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="n">
         <v>3</v>
       </c>
@@ -16598,14 +16598,14 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
       <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="698">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C699" t="inlineStr"/>
@@ -16652,14 +16652,14 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C700" t="inlineStr"/>
       <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="701">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C705" t="inlineStr"/>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C708" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C709" t="inlineStr"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C711" t="inlineStr"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C720" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C721" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -17706,14 +17706,18 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F757" t="n">
@@ -18002,18 +18006,14 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
+      <c r="D771" t="inlineStr"/>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F771" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexFEB</t>
+          <t>Kansas Fed Composite IndexFEB</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -18246,7 +18246,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexFEB</t>
+          <t>Kansas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -18664,18 +18664,18 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F804" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805">
@@ -18686,12 +18686,16 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
       <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr"/>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F805" t="n">
         <v>2</v>
       </c>
@@ -18704,14 +18708,14 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
       <c r="D806" t="inlineStr"/>
       <c r="E806" t="inlineStr"/>
       <c r="F806" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="807">
@@ -18722,14 +18726,18 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr"/>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F807" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="808">
@@ -18740,18 +18748,14 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="809">
@@ -18762,14 +18766,14 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="810">
@@ -18780,16 +18784,12 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="E810" t="inlineStr"/>
       <c r="F810" t="n">
         <v>2</v>
       </c>
@@ -18802,18 +18802,18 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F811" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="812">
@@ -18954,18 +18954,14 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="E819" t="inlineStr"/>
       <c r="F819" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="820">
@@ -18976,14 +18972,14 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr"/>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="821">
@@ -18994,7 +18990,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Construction Spending MoMJAN</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -19012,14 +19008,18 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr"/>
-      <c r="E822" t="inlineStr"/>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F822" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="823">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>Construction Spending MoMJAN</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -19182,14 +19182,14 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
       <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr"/>
       <c r="F831" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="832">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -19218,14 +19218,14 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
       <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr"/>
       <c r="F833" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="834">
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
@@ -19650,14 +19650,18 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
-      <c r="D857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F857" t="n">
@@ -19672,7 +19676,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -19690,7 +19694,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
@@ -19708,14 +19712,18 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
       <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
       <c r="F860" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="861">
@@ -19726,7 +19734,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -19744,22 +19752,14 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
-      <c r="D862" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E862" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
       <c r="F862" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="863">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAR/06</t>
+          <t>15-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAR/06</t>
+          <t>30-Year Mortgage RateMAR/06</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -20124,7 +20124,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Consumer Credit ChangeJAN</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Consumer Credit ChangeJAN</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>

--- a/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
+++ b/Input_data/EST_US_trad_eco_cal_2025-01-02_to_2025-03-07.xlsx
@@ -720,12 +720,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -742,22 +742,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -768,15 +764,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>3</v>
@@ -790,12 +790,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -812,22 +812,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -838,12 +834,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -860,22 +856,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.1M</t>
+          <t>0.7M</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -886,12 +882,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -908,18 +904,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1062,26 +1062,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1092,22 +1092,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1122,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1398,22 +1398,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1424,26 +1428,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1686,22 +1686,18 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -1716,26 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1746,22 +1742,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>8.098M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>7.70M</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1772,22 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1802,26 +1802,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>7.70M</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1832,15 +1828,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1858,26 +1858,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2098,24 +2098,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>201K</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>218K</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
         <v>2</v>
       </c>
@@ -2128,22 +2116,18 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>16.5M</t>
-        </is>
-      </c>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>224K</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2158,26 +2142,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2188,18 +2172,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>16.8M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16.5M</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>224K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2214,14 +2202,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>Continuing Jobless ClaimsDEC/28</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1848K</t>
+        </is>
+      </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2306,18 +2306,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>-0.081M</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2328,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2350,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2372,15 +2376,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2420,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2468,12 +2472,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2490,19 +2494,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2860,22 +2860,26 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2886,26 +2890,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2920,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>-13K</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2950,18 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -2972,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3002,18 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3028,26 +3036,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3282,14 +3282,10 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>1.57B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3326,12 +3322,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,10 +3344,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.57B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3532,26 +3532,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -3562,22 +3562,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3592,22 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3648,18 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,22 +3678,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3708,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3944,18 +3944,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4252,22 +4252,18 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -4278,12 +4274,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,22 +4296,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.961M</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -4326,19 +4318,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-1.304M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="n">
         <v>3</v>
@@ -4352,12 +4340,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4374,18 +4362,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>-1.961M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4396,18 +4388,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4418,15 +4414,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="n">
         <v>3</v>
@@ -4440,12 +4440,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -4556,22 +4556,26 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -4582,22 +4586,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4608,16 +4616,24 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4630,18 +4646,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4652,26 +4676,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4682,26 +4706,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4712,12 +4728,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -4734,26 +4750,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -4764,22 +4780,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4790,26 +4810,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4820,26 +4832,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -4850,16 +4862,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4872,12 +4892,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -4894,26 +4914,18 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4936,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,22 +4962,18 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -4984,26 +4988,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5560,22 +5560,18 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -5586,18 +5582,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -6172,22 +6172,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.148M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6198,18 +6194,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6220,15 +6220,19 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
         <v>3</v>
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6286,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6308,19 +6316,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>6.96%</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
         <v>3</v>
@@ -6334,22 +6338,18 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6448,18 +6448,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -6474,22 +6478,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6504,22 +6508,18 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6870,22 +6870,18 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>New Home SalesDEC</t>
+          <t>New Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>0.67M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>0.64M</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -6900,18 +6896,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>New Home Sales MoMDEC</t>
+          <t>New Home SalesDEC</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0.67M</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>0.64M</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -7178,22 +7178,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -7208,18 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7234,22 +7230,26 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -7260,26 +7260,22 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -7290,18 +7286,22 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -7812,22 +7812,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7838,22 +7834,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,15 +7856,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7908,19 +7904,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,18 +7926,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7956,18 +7952,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8070,18 +8070,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -8096,26 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8156,22 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8182,22 +8182,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8212,26 +8212,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8242,26 +8242,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8272,18 +8272,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -8516,26 +8516,22 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -8546,14 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+          <t>Personal Spending MoMDEC</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -8564,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8594,26 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8624,22 +8632,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8654,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -8684,26 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -8714,18 +8718,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8740,20 +8748,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
         <v>2</v>
       </c>
@@ -8766,22 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8904,26 +8904,26 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -8934,26 +8934,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8964,22 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9016,22 +9016,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9206,18 +9206,18 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F353" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,22 +9258,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -9590,14 +9590,26 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
-      <c r="E369" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
@@ -9608,18 +9620,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9634,22 +9646,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9664,18 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F372" t="n">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -9924,18 +9924,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9946,18 +9950,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9968,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9990,15 +9998,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10012,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10034,19 +10046,15 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10060,22 +10068,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10086,22 +10090,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -10196,22 +10196,22 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -10226,26 +10226,26 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -10256,22 +10256,18 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1886K</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>216.75K</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -10286,22 +10282,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F397" t="n">
@@ -10316,22 +10312,26 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>216.75K</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr"/>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -10536,18 +10536,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>111K</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>141K</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10562,26 +10566,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.6%</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10592,26 +10592,26 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10622,22 +10622,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>3K</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>-2K</t>
-        </is>
-      </c>
+          <t>32K</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10652,26 +10648,26 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10682,18 +10678,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>3K</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-2K</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -10708,22 +10708,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -10738,22 +10738,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>4%</t>
         </is>
       </c>
   